--- a/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-structure/SQLServer_all_types_test2TP02Text.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-structure/SQLServer_all_types_test2TP02Text.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\inputsheet-structure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F84DEBA-FB68-41EF-8E9F-4B91C6680CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE873AEF-39BE-41FB-BFED-99CB32B7C9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4668" yWindow="4536" windowWidth="23160" windowHeight="11256" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all_types_test2" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="ALs2BNum">all_types_test2!$A$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -85,9 +86,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="129">
   <si>
     <t>テーブル名</t>
+  </si>
+  <si>
+    <t>論理名</t>
   </si>
   <si>
     <r>
@@ -102,9 +106,6 @@
     <phoneticPr fontId="0"/>
   </si>
   <si>
-    <t>論理名</t>
-  </si>
-  <si>
     <t>全データ型テストテーブル（SQL Server用）</t>
   </si>
   <si>
@@ -306,6 +307,12 @@
     <t>Bit</t>
   </si>
   <si>
+    <t>Binary(10)</t>
+  </si>
+  <si>
+    <t>VarBinary(255)</t>
+  </si>
+  <si>
     <t>UniqueIdentifier</t>
   </si>
   <si>
@@ -325,6 +332,56 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>エラー予想</t>
+    </r>
+    <rPh sb="3" eb="5">
+      <t>ヨソウ</t>
+    </rPh>
+    <phoneticPr fontId="0"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>実エラー</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <phoneticPr fontId="0"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>齟齬</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ソゴ</t>
+    </rPh>
+    <phoneticPr fontId="0"/>
+  </si>
+  <si>
+    <t>(null)</t>
   </si>
   <si>
     <r>
@@ -346,79 +403,64 @@
     <phoneticPr fontId="0"/>
   </si>
   <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>abcdefghijklmnopqrstu</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>abcdefghij</t>
+  </si>
+  <si>
+    <t>ｱｲｳｴｵｶｷｸｹｺｻｼｽｾｿﾀﾁﾂﾃﾄ</t>
+  </si>
+  <si>
+    <t>ｱｲｳｴｵｶｷｸｹｺ</t>
+  </si>
+  <si>
+    <t>abc123XYZ456def789</t>
+  </si>
+  <si>
+    <t>abc123xyz0</t>
+  </si>
+  <si>
+    <t>aｱ1ｲbｳ2ｴcｵ3ｶdｷ4ｸeｹ</t>
+  </si>
+  <si>
+    <t>aｱ1ｲbｳ2ｴcｵ</t>
+  </si>
+  <si>
+    <t>Ａａ１あいうアイウ亜以宇江尾</t>
+  </si>
+  <si>
+    <t>Ａあア亜字以</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>エラー予想</t>
-    </r>
-    <rPh sb="3" eb="5">
-      <t>ヨソウ</t>
-    </rPh>
-    <phoneticPr fontId="0"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>実エラー</t>
+      <t>Ａａ１あいう
+アイウ亜以宇江尾</t>
     </r>
-    <rPh sb="0" eb="1">
-      <t>ジツ</t>
-    </rPh>
     <phoneticPr fontId="0"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>齟齬</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>ソゴ</t>
-    </rPh>
-    <phoneticPr fontId="0"/>
-  </si>
-  <si>
-    <t>(null)</t>
-  </si>
-  <si>
-    <t>1234567890</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>abcdefghij</t>
-  </si>
-  <si>
-    <t>ｱｲｳｴｵｶｷｸｹｺ</t>
-  </si>
-  <si>
-    <t>abc123xyz0</t>
-  </si>
-  <si>
-    <t>aｱ1ｲbｳ2ｴcｵ</t>
   </si>
   <si>
     <t>Ａあア
 亜字</t>
   </si>
   <si>
-    <t>Ａあア亜字以</t>
+    <t>He said "hello world" to me in Japanese "日本語"</t>
   </si>
   <si>
     <r>
@@ -432,6 +474,12 @@
       <t>Ａあア亜字以ｱｲｳab</t>
     </r>
     <phoneticPr fontId="0"/>
+  </si>
+  <si>
+    <t>it's a test, don't worry about it's value</t>
+  </si>
+  <si>
+    <t>C:\path\to\file, D:\data\file\test.txt</t>
   </si>
   <si>
     <r>
@@ -451,10 +499,19 @@
     <t>He"hi"ij!</t>
   </si>
   <si>
+    <t>\(null)</t>
+  </si>
+  <si>
     <t>it's ok!!</t>
   </si>
   <si>
+    <t>\(NULL)</t>
+  </si>
+  <si>
     <t>a\b\c\d!!</t>
+  </si>
+  <si>
+    <t>null</t>
   </si>
   <si>
     <r>
@@ -480,36 +537,19 @@
     <phoneticPr fontId="0"/>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>abcdefghijklmnopqrstu</t>
-  </si>
-  <si>
-    <t>ｱｲｳｴｵｶｷｸｹｺｻｼｽｾｿﾀﾁﾂﾃﾄ</t>
-  </si>
-  <si>
-    <t>abc123XYZ456def789</t>
-  </si>
-  <si>
-    <t>aｱ1ｲbｳ2ｴcｵ3ｶdｷ4ｸeｹ</t>
-  </si>
-  <si>
-    <t>Ａａ１あいうアイウ亜以宇江尾</t>
-  </si>
-  <si>
-    <t>Ａａ１あいう
-アイウ亜以宇
-江尾</t>
-  </si>
-  <si>
-    <t>He said "hello world" to me in Japanese "日本語"</t>
-  </si>
-  <si>
-    <t>it's a test, don't worry about it's value</t>
-  </si>
-  <si>
-    <t>C:\path\to\file, D:\data\file\test.txt</t>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>(Null)</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>"(null)"</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
   </si>
   <si>
     <r>
@@ -579,6 +619,18 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
+      <t>"(null)"</t>
+    </r>
+    <phoneticPr fontId="0"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
       <t>'(null)</t>
     </r>
     <phoneticPr fontId="0"/>
@@ -608,54 +660,18 @@
     <phoneticPr fontId="0"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>"(null)"</t>
-    </r>
-    <phoneticPr fontId="0"/>
-  </si>
-  <si>
-    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>Binary(10)</t>
-  </si>
-  <si>
-    <t>VarBinary(255)</t>
-  </si>
-  <si>
-    <t>\(null)</t>
-  </si>
-  <si>
-    <t>\(NULL)</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>(Null)</t>
-  </si>
-  <si>
-    <t>"(null)"</t>
-  </si>
-  <si>
     <t>Ａａ１あいう
-アイウ亜以宇江尾</t>
-    <phoneticPr fontId="1"/>
+アイウ亜以宇
+江尾</t>
+  </si>
+  <si>
+    <t>DB種類</t>
+  </si>
+  <si>
+    <t>Microsoft SQL Server</t>
   </si>
 </sst>
 </file>
@@ -792,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
@@ -1030,29 +1046,8 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1440,46 +1435,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD93"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.77734375" style="1" customWidth="1"/>
-    <col min="3" max="5" width="14.77734375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="16.77734375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="8" width="28.77734375" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="10" width="14.77734375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="16.77734375" style="3" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="14.81640625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="18.7265625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="24.7265625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="8" width="28.81640625" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="10" width="14.81640625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="16.81640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.36328125" style="3" customWidth="1"/>
     <col min="13" max="13" width="70" style="3" customWidth="1"/>
-    <col min="14" max="14" width="85.5546875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="14.77734375" style="4" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="14.77734375" style="5" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="18" width="22.77734375" style="6" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="14.77734375" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="21" width="50.77734375" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="36.77734375" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="50.77734375" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="10.77734375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="48.77734375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="2.77734375" style="1" customWidth="1"/>
-    <col min="27" max="29" width="10.77734375" style="42" customWidth="1"/>
-    <col min="30" max="30" width="55.5546875" style="1" customWidth="1"/>
-    <col min="31" max="31" width="9.21875" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.21875" style="1"/>
+    <col min="14" max="14" width="85.54296875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="14.81640625" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="14.81640625" style="5" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="18" width="22.81640625" style="6" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="14.81640625" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="21" width="50.81640625" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="36.81640625" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="50.81640625" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="10.81640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="48.81640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="2.81640625" style="1" customWidth="1"/>
+    <col min="27" max="29" width="10.81640625" style="42" customWidth="1"/>
+    <col min="30" max="30" width="55.54296875" style="1" customWidth="1"/>
+    <col min="31" max="31" width="9.1796875" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>2</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>128</v>
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
@@ -1499,7 +1501,7 @@
       <c r="AB1" s="41"/>
       <c r="AC1" s="41"/>
     </row>
-    <row r="2" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -1522,7 +1524,7 @@
       <c r="AB2" s="41"/>
       <c r="AC2" s="41"/>
     </row>
-    <row r="3" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="34" t="s">
         <v>5</v>
       </c>
@@ -1602,7 +1604,7 @@
       <c r="AB3" s="41"/>
       <c r="AC3" s="41"/>
     </row>
-    <row r="4" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="34" t="s">
         <v>30</v>
       </c>
@@ -1678,7 +1680,7 @@
       <c r="AB4" s="41"/>
       <c r="AC4" s="41"/>
     </row>
-    <row r="5" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>53</v>
       </c>
@@ -1737,16 +1739,16 @@
         <v>69</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="V5" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="X5" s="21"/>
       <c r="Y5" s="21"/>
@@ -1754,75 +1756,75 @@
       <c r="AB5" s="41"/>
       <c r="AC5" s="41"/>
     </row>
-    <row r="6" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P6" s="19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R6" s="20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="W6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="X6" s="21"/>
       <c r="Y6" s="21"/>
@@ -1830,250 +1832,250 @@
       <c r="AB6" s="41"/>
       <c r="AC6" s="41"/>
     </row>
-    <row r="7" spans="1:30" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O7" s="27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P7" s="28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="U7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="W7" s="26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="X7" s="30"/>
       <c r="Y7" s="30"/>
       <c r="AA7" s="43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AB7" s="44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AC7" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AD7" s="45" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="1">
-        <f t="shared" ref="B8:B21" si="0">100+ROW(B8)-7</f>
+        <f t="shared" ref="B8:B39" si="0">100+ROW(B8)-7</f>
         <v>101</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M8" s="46" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X8" s="51"/>
       <c r="Y8" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA8" s="41" t="b">
-        <f t="shared" ref="AA8:AA21" si="1">NOT(ISERROR(FIND("エラー",A8, 1)))</f>
+        <f t="shared" ref="AA8:AA39" si="1">NOT(ISERROR(FIND("エラー",A8, 1)))</f>
         <v>0</v>
       </c>
       <c r="AB8" s="41" t="str">
-        <f t="shared" ref="AB8:AB21" si="2">IF(X8&lt;&gt;"", NOT(X8), "")</f>
+        <f t="shared" ref="AB8:AB39" si="2">IF(X8&lt;&gt;"", NOT(X8), "")</f>
         <v/>
       </c>
       <c r="AC8" s="41" t="str">
-        <f t="shared" ref="AC8:AC21" si="3">IF(AND(AA8&lt;&gt;"", AB8&lt;&gt;""), AA8&lt;&gt;AB8, "")</f>
+        <f t="shared" ref="AC8:AC39" si="3">IF(AND(AA8&lt;&gt;"", AB8&lt;&gt;""), AA8&lt;&gt;AB8, "")</f>
         <v/>
       </c>
       <c r="AD8" s="31"/>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K9" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L9" s="46" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M9" s="46" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X9" s="51"/>
       <c r="Y9" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA9" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2089,78 +2091,78 @@
       </c>
       <c r="AD9" s="31"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L10" s="46" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M10" s="46" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X10" s="51"/>
       <c r="Y10" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA10" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2176,78 +2178,78 @@
       </c>
       <c r="AD10" s="31"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K11" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L11" s="46" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M11" s="46" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X11" s="51"/>
       <c r="Y11" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA11" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2263,78 +2265,78 @@
       </c>
       <c r="AD11" s="31"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K12" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M12" s="46" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X12" s="51"/>
       <c r="Y12" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA12" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2350,78 +2352,78 @@
       </c>
       <c r="AD12" s="31"/>
     </row>
-    <row r="13" spans="1:30" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K13" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L13" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" s="76" t="s">
-        <v>126</v>
+        <v>96</v>
+      </c>
+      <c r="M13" s="70" t="s">
+        <v>97</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X13" s="51"/>
       <c r="Y13" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA13" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2437,78 +2439,78 @@
       </c>
       <c r="AD13" s="31"/>
     </row>
-    <row r="14" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L14" s="46" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M14" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="N14" s="76" t="s">
-        <v>126</v>
+        <v>99</v>
+      </c>
+      <c r="N14" s="70" t="s">
+        <v>97</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X14" s="51"/>
       <c r="Y14" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA14" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2524,339 +2526,339 @@
       </c>
       <c r="AD14" s="31"/>
     </row>
-    <row r="15" spans="1:30" s="70" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="70">
+    <row r="15" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7"/>
+      <c r="B15" s="1">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="C15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="H15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="I15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="K15" s="71" t="s">
-        <v>81</v>
-      </c>
-      <c r="L15" s="72" t="s">
-        <v>90</v>
-      </c>
-      <c r="M15" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="N15" s="71" t="s">
-        <v>103</v>
-      </c>
-      <c r="O15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="P15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="R15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="S15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="T15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="U15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="V15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="W15" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="X15" s="73"/>
-      <c r="Y15" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA15" s="74" t="b">
+      <c r="C15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="L15" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="W15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="X15" s="51"/>
+      <c r="Y15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA15" s="41" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB15" s="74" t="str">
+      <c r="AB15" s="41" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AC15" s="74" t="str">
+      <c r="AC15" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AD15" s="75"/>
-    </row>
-    <row r="16" spans="1:30" s="70" customFormat="1" ht="36" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="70">
+      <c r="AD15" s="31"/>
+    </row>
+    <row r="16" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="7"/>
+      <c r="B16" s="1">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="C16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="H16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="I16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="J16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="71" t="s">
-        <v>81</v>
-      </c>
-      <c r="L16" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="M16" s="71" t="s">
-        <v>105</v>
-      </c>
-      <c r="N16" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="O16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="P16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="R16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="S16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="T16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="U16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="V16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="W16" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="X16" s="73"/>
-      <c r="Y16" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA16" s="74" t="b">
+      <c r="C16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="M16" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="N16" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="V16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="W16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="X16" s="51"/>
+      <c r="Y16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA16" s="41" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="74" t="str">
+      <c r="AB16" s="41" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AC16" s="74" t="str">
+      <c r="AC16" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AD16" s="75"/>
-    </row>
-    <row r="17" spans="1:30" s="70" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="69"/>
-      <c r="B17" s="70">
+      <c r="AD16" s="31"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A17" s="7"/>
+      <c r="B17" s="1">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="J17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="K17" s="71" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17" s="71" t="s">
-        <v>92</v>
-      </c>
-      <c r="M17" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="N17" s="71" t="s">
+      <c r="C17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K17" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="O17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="P17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="R17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="S17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="T17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="U17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="V17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="W17" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="X17" s="73"/>
-      <c r="Y17" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA17" s="74" t="b">
+      <c r="N17" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="T17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="V17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="X17" s="51"/>
+      <c r="Y17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA17" s="41" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="74" t="str">
+      <c r="AB17" s="41" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AC17" s="74" t="str">
+      <c r="AC17" s="41" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AD17" s="75"/>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AD17" s="31"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L18" s="46" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="M18" s="46" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="N18" s="46" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X18" s="51"/>
       <c r="Y18" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA18" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2872,78 +2874,78 @@
       </c>
       <c r="AD18" s="31"/>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" s="7"/>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K19" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L19" s="46" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="M19" s="46" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="N19" s="46" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X19" s="51"/>
       <c r="Y19" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA19" s="41" t="b">
         <f t="shared" si="1"/>
@@ -2959,78 +2961,78 @@
       </c>
       <c r="AD19" s="31"/>
     </row>
-    <row r="20" spans="1:30" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" ht="32.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L20" s="53" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="M20" s="46" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="N20" s="46" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W20" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X20" s="51"/>
       <c r="Y20" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA20" s="41" t="b">
         <f t="shared" si="1"/>
@@ -3046,78 +3048,78 @@
       </c>
       <c r="AD20" s="31"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K21" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L21" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M21" s="46" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="N21" s="46" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X21" s="51"/>
       <c r="Y21" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA21" s="41" t="b">
         <f t="shared" si="1"/>
@@ -3133,1731 +3135,1731 @@
       </c>
       <c r="AD21" s="31"/>
     </row>
-    <row r="22" spans="1:30" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
       <c r="B22" s="1">
-        <f t="shared" ref="B22:B52" si="4">100+ROW(B22)-7</f>
+        <f t="shared" si="0"/>
         <v>115</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K22" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L22" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M22" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N22" s="46" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W22" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X22" s="51"/>
       <c r="Y22" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA22" s="41" t="b">
-        <f t="shared" ref="AA22:AA52" si="5">NOT(ISERROR(FIND("エラー",A22, 1)))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB22" s="41" t="str">
-        <f t="shared" ref="AB22:AB52" si="6">IF(X22&lt;&gt;"", NOT(X22), "")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC22" s="41" t="str">
-        <f t="shared" ref="AC22:AC52" si="7">IF(AND(AA22&lt;&gt;"", AB22&lt;&gt;""), AA22&lt;&gt;AB22, "")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD22" s="31"/>
     </row>
-    <row r="23" spans="1:30" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>116</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K23" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L23" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M23" s="46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N23" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X23" s="51"/>
       <c r="Y23" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA23" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB23" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC23" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD23" s="31"/>
     </row>
-    <row r="24" spans="1:30" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7"/>
       <c r="B24" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>117</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K24" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L24" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M24" s="46" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="N24" s="46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X24" s="51"/>
       <c r="Y24" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA24" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB24" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC24" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD24" s="31"/>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A25" s="7"/>
       <c r="B25" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K25" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L25" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M25" s="46" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="N25" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X25" s="51"/>
       <c r="Y25" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA25" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB25" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC25" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD25" s="31"/>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
       <c r="B26" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>119</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K26" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M26" s="46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N26" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X26" s="51"/>
       <c r="Y26" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA26" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB26" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC26" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD26" s="31"/>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" s="47"/>
       <c r="B27" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J27" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K27" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L27" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M27" s="49" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="N27" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W27" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X27" s="51"/>
       <c r="Y27" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA27" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB27" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC27" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD27" s="31"/>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A28" s="47"/>
       <c r="B28" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>121</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J28" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K28" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L28" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M28" s="49" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="N28" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X28" s="51"/>
       <c r="Y28" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA28" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB28" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC28" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD28" s="31"/>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" s="47"/>
       <c r="B29" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>122</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J29" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K29" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L29" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M29" s="49" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="N29" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X29" s="51"/>
       <c r="Y29" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA29" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB29" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC29" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD29" s="31"/>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A30" s="47"/>
       <c r="B30" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>123</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J30" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K30" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L30" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M30" s="49" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N30" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X30" s="51"/>
       <c r="Y30" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA30" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB30" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC30" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD30" s="31"/>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A31" s="47"/>
       <c r="B31" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>124</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J31" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K31" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L31" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M31" s="49" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="N31" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X31" s="51"/>
       <c r="Y31" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA31" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB31" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC31" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD31" s="31"/>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A32" s="47"/>
       <c r="B32" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>125</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J32" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K32" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L32" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M32" s="50" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="N32" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X32" s="51"/>
       <c r="Y32" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA32" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB32" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC32" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD32" s="31"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A33" s="47"/>
       <c r="B33" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J33" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K33" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L33" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M33" s="50" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="N33" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X33" s="51"/>
       <c r="Y33" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA33" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB33" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC33" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD33" s="31"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A34" s="47"/>
       <c r="B34" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>127</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J34" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K34" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L34" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M34" s="50" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="N34" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W34" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X34" s="51"/>
       <c r="Y34" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA34" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB34" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC34" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD34" s="31"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A35" s="47"/>
       <c r="B35" s="48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J35" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K35" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L35" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M35" s="50" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="N35" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W35" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X35" s="51"/>
       <c r="Y35" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA35" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB35" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC35" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD35" s="31"/>
     </row>
-    <row r="36" spans="1:30" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7"/>
       <c r="B36" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>129</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K36" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L36" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M36" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N36" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X36" s="51"/>
       <c r="Y36" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA36" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB36" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC36" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD36" s="31"/>
     </row>
-    <row r="37" spans="1:30" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7"/>
       <c r="B37" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K37" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L37" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M37" s="46" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N37" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W37" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X37" s="51"/>
       <c r="Y37" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA37" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB37" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC37" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD37" s="31"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A38" s="7"/>
       <c r="B38" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>131</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K38" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L38" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M38" s="46" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="N38" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W38" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X38" s="51"/>
       <c r="Y38" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA38" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB38" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC38" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD38" s="31"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A39" s="7"/>
       <c r="B39" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>132</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K39" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L39" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M39" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N39" s="46" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X39" s="51"/>
       <c r="Y39" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA39" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB39" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AC39" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AD39" s="31"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A40" s="7"/>
       <c r="B40" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="B40:B71" si="4">100+ROW(B40)-7</f>
         <v>133</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K40" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L40" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M40" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N40" s="46" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W40" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X40" s="51"/>
       <c r="Y40" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA40" s="41" t="b">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AA40:AA71" si="5">NOT(ISERROR(FIND("エラー",A40, 1)))</f>
         <v>0</v>
       </c>
       <c r="AB40" s="41" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AB40:AB71" si="6">IF(X40&lt;&gt;"", NOT(X40), "")</f>
         <v/>
       </c>
       <c r="AC40" s="41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AC40:AC71" si="7">IF(AND(AA40&lt;&gt;"", AB40&lt;&gt;""), AA40&lt;&gt;AB40, "")</f>
         <v/>
       </c>
       <c r="AD40" s="31"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A41" s="7"/>
       <c r="B41" s="1">
         <f t="shared" si="4"/>
         <v>134</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K41" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L41" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M41" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N41" s="46" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W41" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X41" s="51"/>
       <c r="Y41" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA41" s="41" t="b">
         <f t="shared" si="5"/>
@@ -4873,78 +4875,78 @@
       </c>
       <c r="AD41" s="31"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A42" s="7"/>
       <c r="B42" s="1">
         <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L42" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M42" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N42" s="46" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="O42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W42" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X42" s="51"/>
       <c r="Y42" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA42" s="41" t="b">
         <f t="shared" si="5"/>
@@ -4960,78 +4962,78 @@
       </c>
       <c r="AD42" s="31"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A43" s="7"/>
       <c r="B43" s="1">
         <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K43" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L43" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M43" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N43" s="46" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W43" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X43" s="51"/>
       <c r="Y43" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA43" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5047,78 +5049,78 @@
       </c>
       <c r="AD43" s="31"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A44" s="7"/>
       <c r="B44" s="1">
         <f t="shared" si="4"/>
         <v>137</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K44" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L44" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M44" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N44" s="46" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W44" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X44" s="51"/>
       <c r="Y44" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA44" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5134,78 +5136,78 @@
       </c>
       <c r="AD44" s="31"/>
     </row>
-    <row r="45" spans="1:30" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" ht="43.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="7"/>
       <c r="B45" s="1">
         <f t="shared" si="4"/>
         <v>138</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K45" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L45" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M45" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N45" s="46" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X45" s="51"/>
       <c r="Y45" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA45" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5221,78 +5223,78 @@
       </c>
       <c r="AD45" s="31"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A46" s="7"/>
       <c r="B46" s="1">
         <f t="shared" si="4"/>
         <v>139</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K46" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L46" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M46" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N46" s="46" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W46" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X46" s="51"/>
       <c r="Y46" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA46" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5308,78 +5310,78 @@
       </c>
       <c r="AD46" s="31"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A47" s="7"/>
       <c r="B47" s="1">
         <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K47" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L47" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M47" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N47" s="46" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W47" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X47" s="51"/>
       <c r="Y47" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA47" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5395,78 +5397,78 @@
       </c>
       <c r="AD47" s="31"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A48" s="7"/>
       <c r="B48" s="1">
         <f t="shared" si="4"/>
         <v>141</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K48" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L48" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M48" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N48" s="46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W48" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X48" s="51"/>
       <c r="Y48" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA48" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5482,78 +5484,78 @@
       </c>
       <c r="AD48" s="31"/>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A49" s="47"/>
       <c r="B49" s="48">
         <f t="shared" si="4"/>
         <v>142</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J49" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K49" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L49" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M49" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N49" s="49" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W49" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X49" s="51"/>
       <c r="Y49" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA49" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5569,78 +5571,78 @@
       </c>
       <c r="AD49" s="31"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A50" s="47"/>
       <c r="B50" s="48">
         <f t="shared" si="4"/>
         <v>143</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J50" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K50" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L50" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M50" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N50" s="49" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="O50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W50" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X50" s="51"/>
       <c r="Y50" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA50" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5656,78 +5658,78 @@
       </c>
       <c r="AD50" s="31"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A51" s="47"/>
       <c r="B51" s="48">
         <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J51" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K51" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L51" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M51" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N51" s="49" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W51" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X51" s="51"/>
       <c r="Y51" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA51" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5743,78 +5745,78 @@
       </c>
       <c r="AD51" s="31"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A52" s="47"/>
       <c r="B52" s="48">
         <f t="shared" si="4"/>
         <v>145</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J52" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K52" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L52" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M52" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N52" s="49" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W52" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X52" s="51"/>
       <c r="Y52" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA52" s="41" t="b">
         <f t="shared" si="5"/>
@@ -5830,2353 +5832,2353 @@
       </c>
       <c r="AD52" s="31"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A53" s="47"/>
       <c r="B53" s="48">
-        <f t="shared" ref="B53:B79" si="8">100+ROW(B53)-7</f>
+        <f t="shared" si="4"/>
         <v>146</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J53" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K53" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L53" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M53" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N53" s="49" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W53" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X53" s="51"/>
       <c r="Y53" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA53" s="41" t="b">
-        <f t="shared" ref="AA53:AA59" si="9">NOT(ISERROR(FIND("エラー",A53, 1)))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB53" s="41" t="str">
-        <f t="shared" ref="AB53:AB59" si="10">IF(X53&lt;&gt;"", NOT(X53), "")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC53" s="41" t="str">
-        <f t="shared" ref="AC53:AC59" si="11">IF(AND(AA53&lt;&gt;"", AB53&lt;&gt;""), AA53&lt;&gt;AB53, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD53" s="31"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A54" s="47"/>
       <c r="B54" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>147</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J54" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K54" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L54" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M54" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N54" s="50" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="O54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W54" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X54" s="51"/>
       <c r="Y54" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA54" s="41" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB54" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC54" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD54" s="31"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A55" s="47"/>
       <c r="B55" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J55" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K55" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L55" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M55" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N55" s="50" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W55" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X55" s="51"/>
       <c r="Y55" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA55" s="41" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB55" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC55" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD55" s="31"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A56" s="47"/>
       <c r="B56" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>149</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J56" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K56" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L56" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M56" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N56" s="50" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="O56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W56" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X56" s="51"/>
       <c r="Y56" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA56" s="41" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB56" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC56" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD56" s="31"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A57" s="47"/>
       <c r="B57" s="48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J57" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K57" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L57" s="49" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M57" s="50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N57" s="50" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="O57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W57" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X57" s="51"/>
       <c r="Y57" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA57" s="41" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB57" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC57" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD57" s="31"/>
     </row>
-    <row r="58" spans="1:30" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:30" ht="57.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7"/>
       <c r="B58" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>151</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K58" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L58" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M58" s="46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N58" s="46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W58" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X58" s="51"/>
       <c r="Y58" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AA58" s="41" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB58" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC58" s="41" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD58" s="31"/>
     </row>
-    <row r="59" spans="1:30" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:30" ht="58.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="54"/>
       <c r="B59" s="55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>152</v>
       </c>
       <c r="C59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K59" s="56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L59" s="56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M59" s="56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N59" s="56" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W59" s="54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X59" s="57"/>
       <c r="Y59" s="55" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="Z59" s="55"/>
       <c r="AA59" s="58" t="b">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB59" s="58" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC59" s="58" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD59" s="59"/>
     </row>
-    <row r="60" spans="1:30" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="60"/>
       <c r="B60" s="60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>153</v>
       </c>
       <c r="C60" s="60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D60" s="60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E60" s="60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F60" s="60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G60" s="61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H60" s="61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I60" s="60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J60" s="60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K60" s="68" t="e">
-        <f t="shared" ref="K60:K79" ca="1" si="12">MID(ALs1BAlphaL, RANDBETWEEN(1, LEN(ALs1BAlphaL)-1),2)&amp;MID(ALs1BKana, RANDBETWEEN(1, LEN(ALs1BKana)-1),2)&amp;MID(ALs1BAlphaS, RANDBETWEEN(1, LEN(ALs1BAlphaS)-1),2)&amp;MID(ALs1BNum, RANDBETWEEN(1, LEN(ALs1BNum)-1),2)</f>
+        <f t="shared" ref="K60:K79" ca="1" si="8">MID(ALs1BAlphaL, RANDBETWEEN(1, LEN(ALs1BAlphaL)-1),2)&amp;MID(ALs1BKana, RANDBETWEEN(1, LEN(ALs1BKana)-1),2)&amp;MID(ALs1BAlphaS, RANDBETWEEN(1, LEN(ALs1BAlphaS)-1),2)&amp;MID(ALs1BNum, RANDBETWEEN(1, LEN(ALs1BNum)-1),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="L60" s="68" t="e">
-        <f t="shared" ref="L60:L79" ca="1" si="13">MID(ALs2BKana, RANDBETWEEN(1, LEN(ALs2BKana)-1),2)&amp;MID(ALs2BAlphaS, RANDBETWEEN(1, LEN(ALs2BAlphaS)-1),2)&amp;MID(ALs1BAlphaL, RANDBETWEEN(1, LEN(ALs1BAlphaL)-1),2)&amp;MID(ALs1BNum, RANDBETWEEN(1, LEN(ALs1BNum)-1),2)</f>
+        <f t="shared" ref="L60:L79" ca="1" si="9">MID(ALs2BKana, RANDBETWEEN(1, LEN(ALs2BKana)-1),2)&amp;MID(ALs2BAlphaS, RANDBETWEEN(1, LEN(ALs2BAlphaS)-1),2)&amp;MID(ALs1BAlphaL, RANDBETWEEN(1, LEN(ALs1BAlphaL)-1),2)&amp;MID(ALs1BNum, RANDBETWEEN(1, LEN(ALs1BNum)-1),2)</f>
         <v>#NUM!</v>
       </c>
       <c r="M60" s="68" t="e">
-        <f t="shared" ref="M60:M79" ca="1" si="14">MID(ALs2BKanji, RANDBETWEEN(1, LEN(ALs2BKanji)-1),20)&amp;MID(ALs2BHirakana, RANDBETWEEN(1, LEN(ALs2BHirakana)-1),20)&amp;MID(ALs2BKana, RANDBETWEEN(1, LEN(ALs2BKana)-1),20)&amp;MID(ALs2BAlphaL, RANDBETWEEN(1, LEN(ALs2BAlphaL)-1),20)&amp;MID(ALs1BKana, RANDBETWEEN(1, LEN(ALs1BKana)-1),20)</f>
+        <f t="shared" ref="M60:M79" ca="1" si="10">MID(ALs2BKanji, RANDBETWEEN(1, LEN(ALs2BKanji)-1),20)&amp;MID(ALs2BHirakana, RANDBETWEEN(1, LEN(ALs2BHirakana)-1),20)&amp;MID(ALs2BKana, RANDBETWEEN(1, LEN(ALs2BKana)-1),20)&amp;MID(ALs2BAlphaL, RANDBETWEEN(1, LEN(ALs2BAlphaL)-1),20)&amp;MID(ALs1BKana, RANDBETWEEN(1, LEN(ALs1BKana)-1),20)</f>
         <v>#NUM!</v>
       </c>
       <c r="N60" s="68" t="e">
-        <f t="shared" ref="N60:N79" ca="1" si="15">MID(ALs2BKana, RANDBETWEEN(1, LEN(ALs2BKana)-1),20)&amp;MID(ALs2BAlphaL, RANDBETWEEN(1, LEN(ALs2BAlphaL)-1),20)&amp;MID(ALs1BKana, RANDBETWEEN(1, LEN(ALs1BKana)-1),20)&amp;MID(ALs2BKanji, RANDBETWEEN(1, LEN(ALs2BKanji)-1),20)&amp;MID(ALs2BHirakana, RANDBETWEEN(1, LEN(ALs2BHirakana)-1),20)</f>
+        <f t="shared" ref="N60:N79" ca="1" si="11">MID(ALs2BKana, RANDBETWEEN(1, LEN(ALs2BKana)-1),20)&amp;MID(ALs2BAlphaL, RANDBETWEEN(1, LEN(ALs2BAlphaL)-1),20)&amp;MID(ALs1BKana, RANDBETWEEN(1, LEN(ALs1BKana)-1),20)&amp;MID(ALs2BKanji, RANDBETWEEN(1, LEN(ALs2BKanji)-1),20)&amp;MID(ALs2BHirakana, RANDBETWEEN(1, LEN(ALs2BHirakana)-1),20)</f>
         <v>#NUM!</v>
       </c>
       <c r="O60" s="63" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P60" s="64" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q60" s="65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R60" s="65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S60" s="60" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T60" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U60" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V60" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W60" s="62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X60" s="60"/>
       <c r="Y60" s="60"/>
       <c r="Z60" s="60"/>
       <c r="AA60" s="66" t="b">
-        <f t="shared" ref="AA60:AA79" si="16">NOT(ISERROR(FIND("エラー",A60, 1)))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB60" s="66" t="str">
-        <f t="shared" ref="AB60:AB79" si="17">IF(X60&lt;&gt;"", NOT(X60), "")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC60" s="66" t="str">
-        <f t="shared" ref="AC60:AC79" si="18">IF(AND(AA60&lt;&gt;"", AB60&lt;&gt;""), AA60&lt;&gt;AB60, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD60" s="60"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B61" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>154</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K61" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L61" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M61" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N61" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P61" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W61" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA61" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB61" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC61" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B62" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>155</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K62" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L62" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M62" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N62" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P62" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W62" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA62" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB62" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC62" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B63" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>156</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K63" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L63" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M63" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N63" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P63" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S63" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W63" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA63" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB63" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC63" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B64" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>157</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K64" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L64" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M64" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N64" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P64" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V64" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W64" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA64" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB64" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC64" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B65" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>158</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K65" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L65" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M65" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N65" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P65" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W65" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA65" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB65" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC65" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B66" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>159</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K66" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L66" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M66" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N66" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P66" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA66" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB66" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC66" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B67" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K67" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L67" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M67" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N67" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA67" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB67" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC67" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B68" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>161</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K68" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L68" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M68" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N68" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P68" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W68" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA68" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB68" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC68" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B69" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>162</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K69" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L69" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M69" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N69" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P69" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T69" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA69" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB69" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC69" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B70" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>163</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K70" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L70" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M70" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N70" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P70" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W70" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA70" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB70" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC70" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B71" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>164</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K71" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L71" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M71" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N71" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P71" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S71" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T71" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U71" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W71" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA71" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB71" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AC71" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B72" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="B72:B79" si="12">100+ROW(B72)-7</f>
         <v>165</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K72" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L72" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M72" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N72" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P72" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T72" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V72" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W72" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA72" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="AA72:AA79" si="13">NOT(ISERROR(FIND("エラー",A72, 1)))</f>
         <v>0</v>
       </c>
       <c r="AB72" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="AB72:AB79" si="14">IF(X72&lt;&gt;"", NOT(X72), "")</f>
         <v/>
       </c>
       <c r="AC72" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" ref="AC72:AC103" si="15">IF(AND(AA72&lt;&gt;"", AB72&lt;&gt;""), AA72&lt;&gt;AB72, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B73" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K73" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L73" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M73" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N73" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P73" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T73" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U73" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V73" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W73" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA73" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB73" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="AC73" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B74" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>167</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K74" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L74" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M74" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N74" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P74" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T74" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U74" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V74" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W74" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA74" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB74" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="AC74" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B75" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K75" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L75" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M75" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N75" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P75" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S75" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T75" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U75" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V75" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W75" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA75" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB75" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="AC75" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B76" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>169</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K76" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L76" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M76" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N76" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P76" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T76" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V76" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W76" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA76" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB76" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="AC76" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B77" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>170</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K77" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L77" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M77" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N77" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P77" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q77" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V77" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W77" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA77" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB77" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="AC77" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B78" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>171</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K78" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L78" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M78" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N78" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P78" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T78" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V78" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W78" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA78" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB78" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="AC78" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B79" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>172</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K79" s="31" t="e">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" ca="1" si="8"/>
         <v>#NUM!</v>
       </c>
       <c r="L79" s="31" t="e">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="9"/>
         <v>#NUM!</v>
       </c>
       <c r="M79" s="31" t="e">
-        <f t="shared" ca="1" si="14"/>
+        <f t="shared" ca="1" si="10"/>
         <v>#NUM!</v>
       </c>
       <c r="N79" s="31" t="e">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="11"/>
         <v>#NUM!</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P79" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S79" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T79" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U79" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V79" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W79" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA79" s="42" t="b">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB79" s="42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="AC79" s="42" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="67"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="67"/>
       <c r="B82" s="67"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="67"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="67"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="67"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="67"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="67"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="67"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="67"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="67"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="67"/>
     </row>
   </sheetData>
